--- a/Table/StageReward.xlsx
+++ b/Table/StageReward.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Public\MiniGame-PushPush\TableData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\MiniGame-PushPush\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E0B5C3-C1E7-4C76-B70B-E439F31F1A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A02691D-6EA8-4379-8BC3-45C023A887FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48" yWindow="1488" windowWidth="17280" windowHeight="8964" xr2:uid="{DE230F5E-A5A3-422C-B9F2-AA52C2C5EF78}"/>
+    <workbookView xWindow="1185" yWindow="3660" windowWidth="26460" windowHeight="15435" xr2:uid="{DE230F5E-A5A3-422C-B9F2-AA52C2C5EF78}"/>
   </bookViews>
   <sheets>
     <sheet name="StageReward" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Coin</t>
+    <t>RewardGroup</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -137,9 +137,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +177,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -283,7 +283,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -425,7 +425,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -434,12 +434,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247803B3-E396-4CB1-BF90-DE5E2BACEB81}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -450,7 +450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -461,7 +461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -469,10 +469,10 @@
         <v>30</v>
       </c>
       <c r="C3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -480,10 +480,10 @@
         <v>50</v>
       </c>
       <c r="C4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -491,10 +491,10 @@
         <v>80</v>
       </c>
       <c r="C5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -502,10 +502,10 @@
         <v>120</v>
       </c>
       <c r="C6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -513,10 +513,10 @@
         <v>170</v>
       </c>
       <c r="C7">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -524,10 +524,10 @@
         <v>230</v>
       </c>
       <c r="C8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -535,10 +535,10 @@
         <v>300</v>
       </c>
       <c r="C9">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -546,10 +546,10 @@
         <v>400</v>
       </c>
       <c r="C10">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -557,10 +557,10 @@
         <v>550</v>
       </c>
       <c r="C11">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -568,10 +568,10 @@
         <v>700</v>
       </c>
       <c r="C12">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -579,10 +579,10 @@
         <v>900</v>
       </c>
       <c r="C13">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -590,7 +590,7 @@
         <v>1200</v>
       </c>
       <c r="C14">
-        <v>65</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
